--- a/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_schedulables.xlsx
+++ b/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_schedulables.xlsx
@@ -468,7 +468,7 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -484,7 +484,7 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -500,7 +500,7 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -508,7 +508,7 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -516,7 +516,7 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -524,7 +524,7 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -532,7 +532,7 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -540,7 +540,7 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -548,7 +548,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -556,7 +556,7 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -564,7 +564,7 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -572,7 +572,7 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -580,7 +580,7 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_schedulables.xlsx
+++ b/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_schedulables.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,16 @@
           <t>gdpa-mapping</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pd-mapping</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bf-mapping</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -430,6 +440,12 @@
       <c r="B2" t="n">
         <v>50</v>
       </c>
+      <c r="C2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -438,6 +454,12 @@
       <c r="B3" t="n">
         <v>50</v>
       </c>
+      <c r="C3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -446,6 +468,12 @@
       <c r="B4" t="n">
         <v>50</v>
       </c>
+      <c r="C4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -454,6 +482,12 @@
       <c r="B5" t="n">
         <v>50</v>
       </c>
+      <c r="C5" t="n">
+        <v>46</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -462,6 +496,12 @@
       <c r="B6" t="n">
         <v>50</v>
       </c>
+      <c r="C6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -470,6 +510,12 @@
       <c r="B7" t="n">
         <v>49</v>
       </c>
+      <c r="C7" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -478,6 +524,12 @@
       <c r="B8" t="n">
         <v>50</v>
       </c>
+      <c r="C8" t="n">
+        <v>42</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -486,6 +538,12 @@
       <c r="B9" t="n">
         <v>48</v>
       </c>
+      <c r="C9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -494,6 +552,12 @@
       <c r="B10" t="n">
         <v>47</v>
       </c>
+      <c r="C10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -502,6 +566,12 @@
       <c r="B11" t="n">
         <v>45</v>
       </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -510,6 +580,12 @@
       <c r="B12" t="n">
         <v>43</v>
       </c>
+      <c r="C12" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -518,6 +594,12 @@
       <c r="B13" t="n">
         <v>40</v>
       </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -526,6 +608,12 @@
       <c r="B14" t="n">
         <v>33</v>
       </c>
+      <c r="C14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -534,6 +622,12 @@
       <c r="B15" t="n">
         <v>29</v>
       </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -542,6 +636,12 @@
       <c r="B16" t="n">
         <v>26</v>
       </c>
+      <c r="C16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -550,6 +650,12 @@
       <c r="B17" t="n">
         <v>20</v>
       </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -558,6 +664,12 @@
       <c r="B18" t="n">
         <v>13</v>
       </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -566,13 +678,25 @@
       <c r="B19" t="n">
         <v>11</v>
       </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -580,7 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_schedulables.xlsx
+++ b/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_schedulables.xlsx
@@ -536,7 +536,7 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
         <v>37</v>
@@ -564,7 +564,7 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
         <v>27</v>
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C12" t="n">
         <v>28</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -592,7 +592,7 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C13" t="n">
         <v>20</v>
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C14" t="n">
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -620,7 +620,7 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
         <v>20</v>
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
         <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -696,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
